--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N99_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N99_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.10224321168349</v>
+        <v>7.329114521898568</v>
       </c>
       <c r="D2" t="n">
-        <v>45.40695313412488</v>
+        <v>7.378629884295294</v>
       </c>
       <c r="E2" t="n">
-        <v>15.77699812366414</v>
+        <v>2.563762195095423</v>
       </c>
       <c r="F2" t="n">
-        <v>15.95644544403803</v>
+        <v>2.59292238465618</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.84368474526248</v>
+        <v>6.962098771105153</v>
       </c>
       <c r="D3" t="n">
-        <v>43.22827483367765</v>
+        <v>7.024594660472618</v>
       </c>
       <c r="E3" t="n">
-        <v>15.77699812366414</v>
+        <v>2.563762195095423</v>
       </c>
       <c r="F3" t="n">
-        <v>15.95644544403803</v>
+        <v>2.59292238465618</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.63348337712474</v>
+        <v>4.65294104878277</v>
       </c>
       <c r="D4" t="n">
-        <v>28.98109828687237</v>
+        <v>4.709428471616761</v>
       </c>
       <c r="E4" t="n">
-        <v>15.77699812366414</v>
+        <v>2.563762195095423</v>
       </c>
       <c r="F4" t="n">
-        <v>15.95644544403803</v>
+        <v>2.59292238465618</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.702888481112464</v>
+        <v>0.9267193781807754</v>
       </c>
       <c r="D5" t="n">
-        <v>5.954792817581944</v>
+        <v>0.9676538328570659</v>
       </c>
       <c r="E5" t="n">
-        <v>15.77699812366414</v>
+        <v>2.563762195095423</v>
       </c>
       <c r="F5" t="n">
-        <v>15.95644544403803</v>
+        <v>2.59292238465618</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.52148950675287</v>
+        <v>2.034742044847342</v>
       </c>
       <c r="D6" t="n">
-        <v>12.02954271152298</v>
+        <v>1.954800690622485</v>
       </c>
       <c r="E6" t="n">
-        <v>15.77699812366414</v>
+        <v>2.563762195095423</v>
       </c>
       <c r="F6" t="n">
-        <v>15.95644544403803</v>
+        <v>2.59292238465618</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
